--- a/artfynd/A 26187-2024 artfynd.xlsx
+++ b/artfynd/A 26187-2024 artfynd.xlsx
@@ -675,43 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119023098</v>
+        <v>119023132</v>
       </c>
       <c r="B2" t="n">
-        <v>100137</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587501</v>
+        <v>587468</v>
       </c>
       <c r="R2" t="n">
-        <v>6350089</v>
+        <v>6350062</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,11 +753,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119023210</v>
+        <v>119023187</v>
       </c>
       <c r="B3" t="n">
-        <v>100137</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,27 +791,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -831,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587474</v>
+        <v>587417</v>
       </c>
       <c r="R3" t="n">
-        <v>6350112</v>
+        <v>6350058</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,7 +871,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119023125</v>
+        <v>119023117</v>
       </c>
       <c r="B4" t="n">
-        <v>109783</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587472</v>
+        <v>587482</v>
       </c>
       <c r="R4" t="n">
-        <v>6350058</v>
+        <v>6350068</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,15 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119023153</v>
+        <v>119023125</v>
       </c>
       <c r="B5" t="n">
-        <v>100137</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587377</v>
+        <v>587472</v>
       </c>
       <c r="R5" t="n">
-        <v>6350034</v>
+        <v>6350058</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,11 +1066,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,42 +1093,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119023083</v>
+        <v>119023088</v>
       </c>
       <c r="B6" t="n">
-        <v>100137</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102225</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221223</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1193,11 +1176,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,37 +1203,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119023119</v>
+        <v>119023109</v>
       </c>
       <c r="B7" t="n">
-        <v>100137</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102225</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>221223</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587482</v>
+        <v>587486</v>
       </c>
       <c r="R7" t="n">
-        <v>6350068</v>
+        <v>6350077</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1332,37 +1305,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119023202</v>
+        <v>119023116</v>
       </c>
       <c r="B8" t="n">
-        <v>100137</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102225</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>221223</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587458</v>
+        <v>587482</v>
       </c>
       <c r="R8" t="n">
-        <v>6350106</v>
+        <v>6350068</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1412,11 +1380,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,15 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119023109</v>
+        <v>119023207</v>
       </c>
       <c r="B9" t="n">
-        <v>101024</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102225</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587486</v>
+        <v>587474</v>
       </c>
       <c r="R9" t="n">
-        <v>6350077</v>
+        <v>6350112</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1551,15 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119023117</v>
+        <v>119023083</v>
       </c>
       <c r="B10" t="n">
-        <v>109783</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,21 +1520,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1595,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587482</v>
+        <v>587503</v>
       </c>
       <c r="R10" t="n">
-        <v>6350068</v>
+        <v>6350122</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1631,6 +1584,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,50 +1616,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119023088</v>
+        <v>119023098</v>
       </c>
       <c r="B11" t="n">
-        <v>101024</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221223</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1710,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587503</v>
+        <v>587501</v>
       </c>
       <c r="R11" t="n">
-        <v>6350122</v>
+        <v>6350089</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1746,6 +1691,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,51 +1723,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119023187</v>
+        <v>119023106</v>
       </c>
       <c r="B12" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1825,10 +1762,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587417</v>
+        <v>587486</v>
       </c>
       <c r="R12" t="n">
-        <v>6350058</v>
+        <v>6350077</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1869,6 +1806,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1887,15 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119023106</v>
+        <v>119023119</v>
       </c>
       <c r="B13" t="n">
-        <v>100137</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,10 +1864,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587486</v>
+        <v>587482</v>
       </c>
       <c r="R13" t="n">
-        <v>6350077</v>
+        <v>6350068</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1994,37 +1927,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119023207</v>
+        <v>119023153</v>
       </c>
       <c r="B14" t="n">
-        <v>101024</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221223</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +1966,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587474</v>
+        <v>587377</v>
       </c>
       <c r="R14" t="n">
-        <v>6350112</v>
+        <v>6350034</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2074,6 +2002,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,12 +2037,7 @@
         <v>119023175</v>
       </c>
       <c r="B15" t="n">
-        <v>100137</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2213,37 +2141,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119023116</v>
+        <v>119023181</v>
       </c>
       <c r="B16" t="n">
-        <v>101024</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221223</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2257,10 +2180,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587482</v>
+        <v>587387</v>
       </c>
       <c r="R16" t="n">
-        <v>6350068</v>
+        <v>6350016</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2293,6 +2216,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,46 +2248,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119023132</v>
+        <v>119023202</v>
       </c>
       <c r="B17" t="n">
-        <v>90491</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5445</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2367,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587468</v>
+        <v>587458</v>
       </c>
       <c r="R17" t="n">
-        <v>6350062</v>
+        <v>6350106</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2403,6 +2323,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2430,15 +2355,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119023181</v>
+        <v>119023210</v>
       </c>
       <c r="B18" t="n">
-        <v>100137</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2474,10 +2394,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587387</v>
+        <v>587474</v>
       </c>
       <c r="R18" t="n">
-        <v>6350016</v>
+        <v>6350112</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2510,11 +2430,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 26187-2024 artfynd.xlsx
+++ b/artfynd/A 26187-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023132</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023187</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023117</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023125</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023088</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023109</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023116</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023207</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023083</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1720,6 +1770,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023098</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1822,6 +1877,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023106</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1924,6 +1984,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023119</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2031,6 +2096,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023153</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2138,6 +2208,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023175</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2245,6 +2320,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023181</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2352,6 +2432,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023202</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2454,8 +2539,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119023210</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>